--- a/output/pdf_financials_xlsx/CPH.xlsx
+++ b/output/pdf_financials_xlsx/CPH.xlsx
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.38</v>
+        <v>10.158</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.457</v>
+        <v>9.462999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.465</v>
+        <v>10.793</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.272</v>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">

--- a/output/pdf_financials_xlsx/CPH.xlsx
+++ b/output/pdf_financials_xlsx/CPH.xlsx
@@ -1059,52 +1059,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.456</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.124</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.066</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.155</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.253</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.488</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.371</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.179</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.464</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2039,52 +2039,52 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.23</v>
+        <v>-2.774</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.715</v>
+        <v>-2.591</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.056</v>
+        <v>0.122</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.311</v>
+        <v>-2.222</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.544</v>
+        <v>2.699</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.411</v>
+        <v>18.664</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.413</v>
+        <v>18.901</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.147</v>
+        <v>-0.776</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-37.657</v>
+        <v>-37.603</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>663.403</v>
+        <v>663.4109999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.164</v>
+        <v>5.359</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>6.313</v>
+        <v>6.492</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>11.059</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>11.479</v>
+        <v>11.943</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>12.681</v>
+        <v>14.551</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.955</v>
+        <v>3.285</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.163</v>
@@ -2155,52 +2155,52 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.764</v>
+        <v>-2.308</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.974</v>
+        <v>-1.85</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.76</v>
+        <v>0.826</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.733</v>
+        <v>-1.644</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.569</v>
+        <v>3.724</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.519</v>
+        <v>19.772</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19.099</v>
+        <v>19.587</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.257</v>
+        <v>3.628</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-36.649</v>
+        <v>-36.595</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>664.234</v>
+        <v>664.242</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.81</v>
+        <v>6.005</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>7.167</v>
+        <v>7.346</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>11.76</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>12.468</v>
+        <v>12.932</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>13.908</v>
+        <v>15.778</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>6.972</v>
+        <v>7.302</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>24.395</v>
@@ -2238,37 +2238,37 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>72.26315204916516</v>
+        <v>73.1998074858391</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>65.35381877908569</v>
+        <v>67.02367916780729</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.465546804615071</v>
+        <v>10.54375308785492</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-124.2338983050848</v>
+        <v>-124.0508474576271</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1656.443890274314</v>
+        <v>1656.463840399002</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>25.53958415754539</v>
+        <v>26.39676469295353</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>31.92285421584785</v>
+        <v>32.72014609594228</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>53.59340108462835</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>60.30471584038693</v>
+        <v>62.54897218863361</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>65.72157641054721</v>
+        <v>74.55817030526416</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>20.89740131283158</v>
+        <v>21.88652099631328</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>48.35384828843829</v>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.881</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>9.006</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>10.328</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>9.635999999999999</v>
@@ -2438,16 +2438,16 @@
         <v>27.182</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>34.486</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>34.486</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>10.357</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>6.346</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>20.548</v>
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.881</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>9.006</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>10.328</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>9.635999999999999</v>
@@ -2554,16 +2554,16 @@
         <v>27.182</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>34.486</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>34.486</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>10.357</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>6.346</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>20.548</v>
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10.158</v>
+        <v>0.277</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9.462999999999999</v>
+        <v>0.457</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.793</v>
+        <v>0.465</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.272</v>
@@ -3250,16 +3250,16 @@
         <v>4.045</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>36.253</v>
+        <v>1.767</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>27.291</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.277</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.352</v>
+        <v>2.006</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.471</v>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -49386,7 +49386,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -54681,7 +54681,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -54887,7 +54887,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -60459,7 +60459,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -61548,7 +61548,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -65279,7 +65279,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -66499,7 +66499,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E584" s="5" t="n">

--- a/output/pdf_financials_xlsx/CPH.xlsx
+++ b/output/pdf_financials_xlsx/CPH.xlsx
@@ -2100,10 +2100,10 @@
         <v>0.466</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.741</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.704</v>
+        <v>0.757</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.578</v>
@@ -2121,16 +2121,16 @@
         <v>4.404</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.008</v>
+        <v>1.121</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.831</v>
+        <v>0.967</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.646</v>
+        <v>0.828</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.854</v>
+        <v>1.187</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0.701</v>
@@ -2158,10 +2158,10 @@
         <v>-2.308</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.781</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.826</v>
+        <v>0.879</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.644</v>
@@ -2179,16 +2179,16 @@
         <v>3.628</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-36.595</v>
+        <v>-36.482</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>664.242</v>
+        <v>664.378</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.005</v>
+        <v>6.187</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>7.346</v>
+        <v>7.679</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>11.76</v>
@@ -2247,16 +2247,16 @@
         <v>10.54375308785492</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-124.0508474576271</v>
+        <v>-123.6677966101695</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1656.463840399002</v>
+        <v>1656.802992518703</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>26.39676469295353</v>
+        <v>27.19679985933448</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>32.72014609594228</v>
+        <v>34.20337624159281</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>53.59340108462835</v>
@@ -6301,40 +6301,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.757</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.045</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.124</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>4.465</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.121</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0.701</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="113">
@@ -25691,7 +25691,11 @@
           <t>Proceeds on disposal property and equipment</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -30003,7 +30007,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30104,7 +30112,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -32278,7 +32286,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -32379,7 +32391,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -37638,7 +37650,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -37737,7 +37753,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -40826,7 +40842,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -41905,7 +41925,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -42006,7 +42030,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -43125,7 +43149,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -43828,7 +43852,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">
@@ -64883,7 +64907,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E568" s="5" t="n">
@@ -68095,7 +68119,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CPH.xlsx
+++ b/output/pdf_financials_xlsx/CPH.xlsx
@@ -1367,10 +1367,10 @@
         <v>6.556</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-1.772</v>
+        <v>2.916</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-264</v>
@@ -1385,10 +1385,10 @@
         <v>-3.071</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.577</v>
+        <v>-3.413</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.904</v>
+        <v>0.847</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>4.965</v>
@@ -2299,10 +2299,10 @@
         <v>35.60914670577372</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.792212024113398</v>
+        <v>1.955140389941889</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-154.4899738448126</v>
+        <v>-254.2284219703574</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-701.0648750564304</v>
@@ -2317,10 +2317,10 @@
         <v>48.64565182955806</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>140.8536033999457</v>
+        <v>30.8617415679537</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>77.56773238086942</v>
+        <v>7.378691523651885</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>39.15306363851431</v>
@@ -3724,25 +3724,25 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -3782,25 +3782,25 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.303</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
@@ -4391,19 +4391,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.678</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>2.629</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4592,19 +4592,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="71">
@@ -4650,19 +4650,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="72">
@@ -4882,19 +4882,19 @@
         <v>16.615</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>6.739</v>
+        <v>6.683</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>5.262</v>
+        <v>5.161</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.656</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>14.001</v>
+        <v>13.718</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>18.651</v>
+        <v>18.362</v>
       </c>
     </row>
     <row r="76">
@@ -5191,26 +5191,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.001439699719772733</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.001576154806491885</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.001167411823149528</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.3908425588462328</v>
+        <v>0.3936077699500699</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.0396058426539083</v>
+        <v>0.0418950603593042</v>
       </c>
     </row>
     <row r="81">
@@ -7247,19 +7241,19 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.762</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-7.394</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.075</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.148</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-6.5</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -7277,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.173</v>
       </c>
     </row>
     <row r="117">
@@ -8047,20 +8041,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>34.004</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>-3.543</v>
@@ -8401,30 +8389,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>-0.828</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>6.843</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>24.738</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>7.593</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>18.128</v>
@@ -10030,7 +10008,11 @@
           <t>Current portion of lease obligation (Notes 6 &amp; 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11794,7 +11776,11 @@
           <t>Current portion of lease obligation (Note 10)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12905,7 +12891,11 @@
           <t>Current portion of lease obligation (note 10)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -25796,7 +25786,11 @@
           <t>Purchase of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -33660,7 +33654,11 @@
           <t>Acquisition of intangible assets 11</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -37153,7 +37151,11 @@
           <t>Deferred income tax expense 3,254</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -38644,7 +38646,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -39846,7 +39852,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -40044,7 +40054,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -42741,7 +42755,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -43349,7 +43367,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -47026,7 +47048,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -47125,7 +47151,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -49897,7 +49927,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -49996,7 +50030,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -51901,7 +51939,11 @@
           <t>Current income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -52000,7 +52042,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -54303,7 +54349,11 @@
           <t>Current income tax (recovery) expense (note 16)</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -54402,7 +54452,11 @@
           <t>Deferred income tax (recovery) expense (note 16)</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -54501,7 +54555,11 @@
           <t>Total income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -63792,7 +63850,11 @@
           <t>Income taxes (recovery) 16</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -65606,7 +65668,11 @@
           <t>Income taxes (recovery) 16</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>
